--- a/Database_Tracking_MNS.xlsx
+++ b/Database_Tracking_MNS.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F5DC3A7-C170-43C1-A232-2A20089EA6E1}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIOVANY HAM\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BF1517-7B8F-4BCF-B4EF-AA9AA5A8DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dokumen" sheetId="1" r:id="rId1"/>
@@ -23,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>department</t>
   </si>
@@ -95,13 +98,16 @@
   </si>
   <si>
     <t>MNSbtg2026</t>
+  </si>
+  <si>
+    <t>Ready To Take</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,18 +545,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -594,13 +600,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
@@ -633,13 +639,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A5C29F-0D89-4B1F-B6EA-65CB69E87B7C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -647,7 +653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -655,7 +661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>

--- a/Database_Tracking_MNS.xlsx
+++ b/Database_Tracking_MNS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIOVANY HAM\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BF1517-7B8F-4BCF-B4EF-AA9AA5A8DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C4A7E6-5495-47E4-818B-8318BE09519B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="21">
   <si>
     <t>department</t>
   </si>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BA69FFC3-02AA-45D6-B34F-642E421883DF}" name="Table2" displayName="Table2" ref="A1:H3" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:H3" xr:uid="{BA69FFC3-02AA-45D6-B34F-642E421883DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BA69FFC3-02AA-45D6-B34F-642E421883DF}" name="Table2" displayName="Table2" ref="A1:H25" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H25" xr:uid="{BA69FFC3-02AA-45D6-B34F-642E421883DF}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BF7653B7-52BE-4CA2-A4B7-F27F7B7411BC}" name="department"/>
     <tableColumn id="2" xr3:uid="{428E8D57-8B44-42BE-9651-7351C5CF652E}" name="pic"/>
@@ -544,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -627,6 +627,534 @@
         <v>12</v>
       </c>
       <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3">
+        <v>46210</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database_Tracking_MNS.xlsx
+++ b/Database_Tracking_MNS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIOVANY HAM\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIOVANY HAM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C4A7E6-5495-47E4-818B-8318BE09519B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C9A822-D11F-4A04-BE91-B69CF1F93987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dokumen" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="22">
   <si>
     <t>department</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Ready To Take</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1194,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>19</v>
